--- a/Data/Building/Lab.HumanState.xlsx
+++ b/Data/Building/Lab.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:I155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709250248</v>
+        <v>1711842014</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709250671</v>
+        <v>1711842324</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709250914</v>
+        <v>1711842731</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709278871</v>
+        <v>1711873684</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709279528</v>
+        <v>1711874140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709279995</v>
+        <v>1711874723</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709244511</v>
+        <v>1711875384</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709272219</v>
+        <v>1711875738</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709331090</v>
+        <v>1711923341</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709358837</v>
+        <v>1711948737</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709359356</v>
+        <v>1711949220</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +840,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709359852</v>
+        <v>1711949592</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +873,11 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709417279</v>
+        <v>1711950276</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +910,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709443831</v>
+        <v>1711950629</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +943,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +966,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709443932</v>
+        <v>1712009483</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +980,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +999,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709443951</v>
+        <v>1712009890</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1013,11 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1036,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709444031</v>
+        <v>1712010106</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1050,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1069,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709445973</v>
+        <v>1712037423</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1083,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1102,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709446697</v>
+        <v>1712037760</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1116,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1135,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709447180</v>
+        <v>1712038671</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1149,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1168,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709447821</v>
+        <v>1712096062</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1182,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1201,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709448183</v>
+        <v>1712126175</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1215,11 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1238,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709503070</v>
+        <v>1712126400</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1252,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1271,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709532712</v>
+        <v>1712127011</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1285,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1308,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709533108</v>
+        <v>1712127601</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1322,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1341,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709533767</v>
+        <v>1712128134</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1355,11 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1378,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709534419</v>
+        <v>1712181266</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1392,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1411,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709534978</v>
+        <v>1712210256</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1425,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1448,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709590847</v>
+        <v>1712210292</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1462,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1481,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709622481</v>
+        <v>1712211063</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1495,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1518,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709623098</v>
+        <v>1712211543</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1532,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1551,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709623599</v>
+        <v>1712212180</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1565,11 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1588,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709683713</v>
+        <v>1712267314</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1602,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1621,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709700735</v>
+        <v>1712297666</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1635,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1654,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709701365</v>
+        <v>1712298154</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1668,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1687,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709701726</v>
+        <v>1712298796</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1701,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1720,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709770622</v>
+        <v>1712299366</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1734,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1753,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709773674</v>
+        <v>1712299923</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1767,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1786,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709773776</v>
+        <v>1712360362</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1800,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1819,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709785357</v>
+        <v>1712378259</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1833,11 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1856,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709785521</v>
+        <v>1712379293</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1870,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1889,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709787678</v>
+        <v>1712379877</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1903,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1926,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709848521</v>
+        <v>1712451415</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1940,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1959,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709873026</v>
+        <v>1712465490</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1973,11 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1996,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709873240</v>
+        <v>1712529440</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +2010,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2029,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709873853</v>
+        <v>1712555776</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2043,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2062,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709874352</v>
+        <v>1712555791</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2076,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2095,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709874896</v>
+        <v>1712556469</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2109,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2128,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709936315</v>
+        <v>1712557142</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2142,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2161,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709962965</v>
+        <v>1712557695</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2175,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2194,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709963541</v>
+        <v>1712615505</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2208,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2227,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709963917</v>
+        <v>1712615663</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2241,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2260,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710023477</v>
+        <v>1712616112</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2274,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2293,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710051635</v>
+        <v>1712643379</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2307,11 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2330,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710051977</v>
+        <v>1712644104</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2344,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2363,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710054544</v>
+        <v>1712644725</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2377,11 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2400,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710054981</v>
+        <v>1712703815</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2414,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2433,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710055541</v>
+        <v>1712730688</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2447,11 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2470,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710109226</v>
+        <v>1712730922</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2484,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2503,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710138589</v>
+        <v>1712731460</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2517,11 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2540,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710138677</v>
+        <v>1712732141</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2554,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2573,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710139032</v>
+        <v>1712732651</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2587,11 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2610,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710195241</v>
+        <v>1712789442</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2624,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2643,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710225041</v>
+        <v>1712814374</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2657,11 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2680,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710225221</v>
+        <v>1712814581</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2694,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2713,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710225644</v>
+        <v>1712814602</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2727,11 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2750,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710225730</v>
+        <v>1712814738</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2764,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2783,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710226114</v>
+        <v>1712815224</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2797,11 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2820,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710226736</v>
+        <v>1712815782</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2834,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2853,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710227318</v>
+        <v>1712816264</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2867,11 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2890,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710290016</v>
+        <v>1712874304</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2904,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2923,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710306585</v>
+        <v>1712900752</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2937,11 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2960,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710375001</v>
+        <v>1712900810</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2974,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2993,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710393125</v>
+        <v>1712902754</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +3007,11 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +3030,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710455175</v>
+        <v>1712903590</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3044,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3063,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710482655</v>
+        <v>1712904013</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3077,11 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3100,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710483367</v>
+        <v>1712904563</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3114,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3133,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710483532</v>
+        <v>1712905068</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3147,11 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3170,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710540423</v>
+        <v>1712968478</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3184,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3203,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710540735</v>
+        <v>1712985714</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3217,11 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3240,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710540871</v>
+        <v>1712986600</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3254,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3273,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710570636</v>
+        <v>1712986840</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3287,11 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3310,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710571137</v>
+        <v>1713051269</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3324,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3343,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710571825</v>
+        <v>1713068500</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3357,11 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3380,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710628848</v>
+        <v>1713069042</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3394,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3413,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710657482</v>
+        <v>1713069666</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3427,11 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3450,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710714383</v>
+        <v>1713133143</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3464,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3483,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710741476</v>
+        <v>1713160270</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3497,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3516,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710741898</v>
+        <v>1713218609</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3530,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3549,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710742296</v>
+        <v>1713219275</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3563,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3582,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710800093</v>
+        <v>1713219285</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3596,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3615,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710828287</v>
+        <v>1713244029</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3629,11 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3652,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710891667</v>
+        <v>1713305780</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3666,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3685,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710910330</v>
+        <v>1713305945</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3699,11 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3722,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710977982</v>
+        <v>1713305959</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3736,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3755,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710991593</v>
+        <v>1713328990</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3769,11 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3792,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710992145</v>
+        <v>1713329472</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3806,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3825,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710997027</v>
+        <v>1713331466</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3839,11 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3862,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711058015</v>
+        <v>1713332109</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3876,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3895,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711087674</v>
+        <v>1713332645</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3909,11 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3932,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711088246</v>
+        <v>1713333257</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3946,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3965,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711088763</v>
+        <v>1713333805</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3979,11 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +4002,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711089488</v>
+        <v>1713391029</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +4016,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +4035,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711090123</v>
+        <v>1713414768</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +4049,11 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +4072,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711145752</v>
+        <v>1713414799</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4086,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4105,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711174698</v>
+        <v>1713415364</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4119,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4142,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711175132</v>
+        <v>1713415975</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4156,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711175629</v>
+        <v>1713416543</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4189,11 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4212,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711232179</v>
+        <v>1713479004</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4226,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4245,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711260940</v>
+        <v>1713503680</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4259,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4278,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711261319</v>
+        <v>1713503854</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4292,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4311,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711261348</v>
+        <v>1713504373</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4325,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4344,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711261574</v>
+        <v>1713504711</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4358,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4377,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711261948</v>
+        <v>1713505392</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4391,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4410,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711318583</v>
+        <v>1713569983</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4424,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4443,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711345766</v>
+        <v>1713586905</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4457,11 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4480,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711346382</v>
+        <v>1713587349</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4494,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4513,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711346874</v>
+        <v>1713587889</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4527,11 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4550,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1711405224</v>
+        <v>1713657935</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4564,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4583,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711434259</v>
+        <v>1713674323</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4597,11 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4620,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711434729</v>
+        <v>1713737352</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4634,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4653,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711435402</v>
+        <v>1713737776</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4667,11 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4690,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711436182</v>
+        <v>1713737838</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4704,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4723,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711436625</v>
+        <v>1713762133</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4737,11 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4760,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711498209</v>
+        <v>1713762539</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4774,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4793,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711517696</v>
+        <v>1713762657</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4807,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4830,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711586215</v>
+        <v>1713762784</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4844,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4863,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711590742</v>
+        <v>1713763289</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4877,11 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4900,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711591124</v>
+        <v>1713823304</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4914,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4933,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711604218</v>
+        <v>1713853209</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4947,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4966,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711604546</v>
+        <v>1713909782</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4980,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4999,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711605196</v>
+        <v>1713937139</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +5013,769 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1713937175</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1713938189</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1713938324</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1713938746</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1713938752</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1713939369</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1713995789</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1714020195</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1714020217</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1714020326</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1714020875</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1714021340</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1714082829</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1714106927</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1714107519</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1714107915</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1714108569</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1714109128</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1714175474</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1714190746</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1714261867</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Detected</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HumanDetected_Change</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1714279864</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Lab.HumanState.state: Undetected</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
